--- a/data/focus_groups/focus_group_ports.xlsx
+++ b/data/focus_groups/focus_group_ports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/focus_groups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354AF278-E149-A242-87A9-C244D5639133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48848C73-24CA-B842-B49F-A2388A7B6BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" xr2:uid="{7398944A-41C7-9044-8574-B9C64E04E2AB}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>Morro Bay</t>
   </si>
   <si>
-    <t>Brookings</t>
-  </si>
-  <si>
     <t>lat_dd</t>
   </si>
   <si>
@@ -54,6 +51,9 @@
   </si>
   <si>
     <t>Eureka</t>
+  </si>
+  <si>
+    <t>Newport</t>
   </si>
 </sst>
 </file>
@@ -446,10 +446,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -465,7 +465,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>40.801943999999999</v>
@@ -476,13 +476,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>42.067500000000003</v>
+        <v>44.638333000000003</v>
       </c>
       <c r="C4">
-        <v>-124.303056</v>
+        <v>-124.051389</v>
       </c>
     </row>
   </sheetData>
